--- a/ets/rendiconti2020/rendiconti-excel-word/rendiconto-per-cassa-modello-excel.xlsx
+++ b/ets/rendiconti2020/rendiconti-excel-word/rendiconto-per-cassa-modello-excel.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\michael.mercurio\Documents\GitHub\Italia\ets\rendiconti2020\rendiconti-excel-word\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\michael.mercurio\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E84D28D-9E7D-47FC-A5E1-FC4FB1F37430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D42A45A-4573-452C-9AF9-0C63E8EE5D26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FF94FDBB-7E1C-4349-A12A-5CA933A991FE}"/>
   </bookViews>
@@ -16,9 +16,9 @@
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Foglio1!$A$7:$G$133</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Foglio1!$A$8:$G$139</definedName>
     <definedName name="FormatoStampa">Foglio1!#REF!</definedName>
-    <definedName name="ZonaInserimento">Foglio1!$B$14:$C$18,Foglio1!$B$28:$C$32,Foglio1!$B$38:$C$40,Foglio1!$B$45:$C$49,Foglio1!$B$54:$C$58,Foglio1!$B$68:$C$71,Foglio1!$F$14:$G$23,Foglio1!$F$28:$G$33,Foglio1!$F$38:$G$40,Foglio1!$F$45:$G$49,Foglio1!$F$54:$G$55,Foglio1!$F$63:$G$63,Foglio1!$F$68:$G$71,Foglio1!$F$73:$G$73,Foglio1!$F$84:$G$85,Foglio1!$F$89:$G$90,Foglio1!$B$89:$C$90</definedName>
+    <definedName name="ZonaInserimento">Foglio1!$B$15:$C$19,Foglio1!$B$29:$C$33,Foglio1!$B$39:$C$41,Foglio1!$B$46:$C$50,Foglio1!$B$55:$C$59,Foglio1!$B$69:$C$72,Foglio1!$F$15:$G$24,Foglio1!$F$29:$G$34,Foglio1!$F$39:$G$41,Foglio1!$F$46:$G$50,Foglio1!$F$55:$G$56,Foglio1!$F$64:$G$64,Foglio1!$F$69:$G$72,Foglio1!$F$74:$G$74,Foglio1!$F$85:$G$86,Foglio1!$F$90:$G$91,Foglio1!$B$90:$C$91</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="120">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -323,9 +323,6 @@
   </si>
   <si>
     <t>https://www.lavoro.gov.it/documenti-e-norme/normative/Documents/2020/DM-05032020-Adozione-modulistica-di-bilancioi-Enti-del-Terzo-Settore.pdf</t>
-  </si>
-  <si>
-    <t>Rendiconto per Cassa secondo modello D. (vedi pagina 13 del)</t>
   </si>
   <si>
     <t xml:space="preserve">Impostazioni </t>
@@ -409,6 +406,21 @@
   </si>
   <si>
     <t>In questo modo potrai anche ottenere in automatico il Rendiconto per cassa e altri rendiconti.</t>
+  </si>
+  <si>
+    <t>ETS fino a 60.000 €</t>
+  </si>
+  <si>
+    <t>https://www.banana.ch/apps/it/node/10168</t>
+  </si>
+  <si>
+    <t>Per Micro ETS fino a 60.000 €, mettiamo a disposizione anche il modello Excel del Rendiconto per cassa in forma aggregata (Modello E):</t>
+  </si>
+  <si>
+    <t>Rendiconto per Cassa secondo modello D. (vedi pagina 13 del documento qui sotto)</t>
+  </si>
+  <si>
+    <t>Rendiconto per Cassa ETS secondo modello D. del Ministero</t>
   </si>
 </sst>
 </file>
@@ -609,21 +621,21 @@
     <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
@@ -967,7 +979,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5901BA8-36CC-4DBE-B6A9-97354061FBEE}">
-  <dimension ref="A1:I133"/>
+  <dimension ref="A1:I139"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="45.6796875" customWidth="1"/>
@@ -981,121 +993,106 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A1" s="24" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="16" x14ac:dyDescent="0.75">
-      <c r="A2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B2" s="22">
-        <v>46022</v>
+      <c r="A1" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A2" s="24" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="16" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B3" s="22">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="16" x14ac:dyDescent="0.75">
+      <c r="A4" t="s">
         <v>92</v>
       </c>
-      <c r="B3" s="22">
-        <v>45657</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" s="3" customFormat="1" ht="21" x14ac:dyDescent="1">
-      <c r="A7" s="29" t="s">
+      <c r="B4" s="22">
+        <v>46022</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" s="3" customFormat="1" ht="21" x14ac:dyDescent="1">
+      <c r="A8" s="37" t="s">
         <v>86</v>
       </c>
-      <c r="B7" s="30"/>
-      <c r="C7" s="30"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="30"/>
-    </row>
-    <row r="8" spans="1:7" ht="21" x14ac:dyDescent="1">
-      <c r="A8" s="3" t="s">
+      <c r="B8" s="36"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+    </row>
+    <row r="9" spans="1:7" ht="21" x14ac:dyDescent="1">
+      <c r="A9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B8" s="21">
-        <f>B2</f>
-        <v>46022</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="21" x14ac:dyDescent="1">
-      <c r="A9" t="s">
-        <v>104</v>
-      </c>
-      <c r="B9" s="21"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="B10" s="19"/>
+      <c r="B9" s="21">
+        <f>B3</f>
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="21" x14ac:dyDescent="1">
+      <c r="A10" t="s">
+        <v>103</v>
+      </c>
+      <c r="B10" s="21"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.75">
       <c r="B11" s="19"/>
     </row>
-    <row r="12" spans="1:7" s="5" customFormat="1" ht="16" x14ac:dyDescent="0.8">
-      <c r="A12" s="6" t="s">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="B12" s="19"/>
+    </row>
+    <row r="13" spans="1:7" s="5" customFormat="1" ht="16" x14ac:dyDescent="0.8">
+      <c r="A13" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="16">
-        <f>B2</f>
+      <c r="B13" s="16">
+        <f>B3</f>
+        <v>46387</v>
+      </c>
+      <c r="C13" s="16">
+        <f>B4</f>
         <v>46022</v>
       </c>
-      <c r="C12" s="16">
+      <c r="E13" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" s="16">
         <f>B3</f>
-        <v>45657</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" s="16">
-        <f>B2</f>
+        <v>46387</v>
+      </c>
+      <c r="G13" s="16">
+        <f>B4</f>
         <v>46022</v>
       </c>
-      <c r="G12" s="16">
-        <f>B3</f>
-        <v>45657</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A13" s="4" t="s">
+    </row>
+    <row r="14" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.75">
+      <c r="A14" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E14" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A14" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="20">
-        <v>0</v>
-      </c>
-      <c r="C14" s="20">
-        <v>0</v>
-      </c>
-      <c r="E14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="20">
-        <v>0</v>
-      </c>
-      <c r="G14" s="20">
-        <v>0</v>
-      </c>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B15" s="20">
         <v>0</v>
@@ -1104,7 +1101,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F15" s="20">
         <v>0</v>
@@ -1115,7 +1112,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B16" s="20">
         <v>0</v>
@@ -1124,7 +1121,7 @@
         <v>0</v>
       </c>
       <c r="E16" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F16" s="20">
         <v>0</v>
@@ -1135,7 +1132,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B17" s="20">
         <v>0</v>
@@ -1144,7 +1141,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F17" s="20">
         <v>0</v>
@@ -1155,27 +1152,36 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="20">
+        <v>0</v>
+      </c>
+      <c r="C18" s="20">
+        <v>0</v>
+      </c>
+      <c r="E18" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18" s="20">
+        <v>0</v>
+      </c>
+      <c r="G18" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A19" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="20">
-        <v>0</v>
-      </c>
-      <c r="C18" s="20">
-        <v>0</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="B19" s="20">
+        <v>0</v>
+      </c>
+      <c r="C19" s="20">
+        <v>0</v>
+      </c>
+      <c r="E19" t="s">
         <v>19</v>
-      </c>
-      <c r="F18" s="20">
-        <v>0</v>
-      </c>
-      <c r="G18" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="E19" t="s">
-        <v>20</v>
       </c>
       <c r="F19" s="20">
         <v>0</v>
@@ -1186,7 +1192,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.75">
       <c r="E20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F20" s="20">
         <v>0</v>
@@ -1197,7 +1203,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.75">
       <c r="E21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F21" s="20">
         <v>0</v>
@@ -1208,7 +1214,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.75">
       <c r="E22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F22" s="20">
         <v>0</v>
@@ -1219,95 +1225,86 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.75">
       <c r="E23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F23" s="20">
+        <v>0</v>
+      </c>
+      <c r="G23" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="E24" t="s">
         <v>24</v>
       </c>
-      <c r="F23" s="20">
-        <v>0</v>
-      </c>
-      <c r="G23" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A24" s="11" t="s">
+      <c r="F24" s="20">
+        <v>0</v>
+      </c>
+      <c r="G24" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A25" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B24" s="12">
-        <f>SUM(B14:B18)</f>
-        <v>0</v>
-      </c>
-      <c r="C24" s="12">
-        <f>SUM(C14:C18)</f>
-        <v>0</v>
-      </c>
-      <c r="D24" s="4"/>
-      <c r="E24" s="11" t="s">
+      <c r="B25" s="12">
+        <f>SUM(B15:B19)</f>
+        <v>0</v>
+      </c>
+      <c r="C25" s="12">
+        <f>SUM(C15:C19)</f>
+        <v>0</v>
+      </c>
+      <c r="D25" s="4"/>
+      <c r="E25" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="F24" s="12">
-        <f>SUM(F14:F23)</f>
-        <v>0</v>
-      </c>
-      <c r="G24" s="12">
-        <f>SUM(G14:G23)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A25" s="28" t="s">
+      <c r="F25" s="12">
+        <f>SUM(F15:F24)</f>
+        <v>0</v>
+      </c>
+      <c r="G25" s="12">
+        <f>SUM(G15:G24)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A26" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="28"/>
-      <c r="C25" s="28"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="10">
-        <f>F24-B24</f>
-        <v>0</v>
-      </c>
-      <c r="G25" s="10">
-        <f>G24-C24</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
+      <c r="B26" s="34"/>
+      <c r="C26" s="34"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="34"/>
+      <c r="F26" s="10">
+        <f>F25-B25</f>
+        <v>0</v>
+      </c>
+      <c r="G26" s="10">
+        <f>G25-C25</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="7"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A28" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E28" s="4" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A28" t="s">
-        <v>10</v>
-      </c>
-      <c r="B28" s="20">
-        <v>0</v>
-      </c>
-      <c r="C28" s="20">
-        <v>0</v>
-      </c>
-      <c r="E28" t="s">
-        <v>28</v>
-      </c>
-      <c r="F28" s="20">
-        <v>0</v>
-      </c>
-      <c r="G28" s="20">
-        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B29" s="20">
         <v>0</v>
@@ -1316,7 +1313,7 @@
         <v>0</v>
       </c>
       <c r="E29" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F29" s="20">
         <v>0</v>
@@ -1327,7 +1324,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A30" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B30" s="20">
         <v>0</v>
@@ -1336,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="E30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F30" s="20">
         <v>0</v>
@@ -1347,7 +1344,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A31" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B31" s="20">
         <v>0</v>
@@ -1356,7 +1353,7 @@
         <v>0</v>
       </c>
       <c r="E31" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F31" s="20">
         <v>0</v>
@@ -1367,115 +1364,115 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A32" t="s">
+        <v>16</v>
+      </c>
+      <c r="B32" s="20">
+        <v>0</v>
+      </c>
+      <c r="C32" s="20">
+        <v>0</v>
+      </c>
+      <c r="E32" t="s">
+        <v>31</v>
+      </c>
+      <c r="F32" s="20">
+        <v>0</v>
+      </c>
+      <c r="G32" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A33" t="s">
         <v>18</v>
       </c>
-      <c r="B32" s="20">
-        <v>0</v>
-      </c>
-      <c r="C32" s="20">
-        <v>0</v>
-      </c>
-      <c r="E32" t="s">
+      <c r="B33" s="20">
+        <v>0</v>
+      </c>
+      <c r="C33" s="20">
+        <v>0</v>
+      </c>
+      <c r="E33" t="s">
         <v>32</v>
       </c>
-      <c r="F32" s="20">
-        <v>0</v>
-      </c>
-      <c r="G32" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="E33" t="s">
+      <c r="F33" s="20">
+        <v>0</v>
+      </c>
+      <c r="G33" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="E34" t="s">
         <v>33</v>
       </c>
-      <c r="F33" s="20">
-        <v>0</v>
-      </c>
-      <c r="G33" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A34" s="11" t="s">
+      <c r="F34" s="20">
+        <v>0</v>
+      </c>
+      <c r="G34" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A35" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B34" s="12">
-        <f>SUM(B28:B32)</f>
-        <v>0</v>
-      </c>
-      <c r="C34" s="12">
-        <f>SUM(C28:C32)</f>
-        <v>0</v>
-      </c>
-      <c r="D34" s="4"/>
-      <c r="E34" s="11" t="s">
+      <c r="B35" s="12">
+        <f>SUM(B29:B33)</f>
+        <v>0</v>
+      </c>
+      <c r="C35" s="12">
+        <f>SUM(C29:C33)</f>
+        <v>0</v>
+      </c>
+      <c r="D35" s="4"/>
+      <c r="E35" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="F34" s="12">
-        <f>SUM(F28:F33)</f>
-        <v>0</v>
-      </c>
-      <c r="G34" s="12">
-        <f>SUM(G28:G33)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A35" s="28" t="s">
+      <c r="F35" s="12">
+        <f>SUM(F29:F34)</f>
+        <v>0</v>
+      </c>
+      <c r="G35" s="12">
+        <f>SUM(G29:G34)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A36" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="28"/>
-      <c r="C35" s="28"/>
-      <c r="D35" s="28"/>
-      <c r="E35" s="28"/>
-      <c r="F35" s="10">
-        <f>F34-B34</f>
-        <v>0</v>
-      </c>
-      <c r="G35" s="10">
-        <f>G34-C34</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A36" s="7"/>
-      <c r="B36" s="7"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
+      <c r="B36" s="34"/>
+      <c r="C36" s="34"/>
+      <c r="D36" s="34"/>
+      <c r="E36" s="34"/>
+      <c r="F36" s="10">
+        <f>F35-B35</f>
+        <v>0</v>
+      </c>
+      <c r="G36" s="10">
+        <f>G35-C35</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="7"/>
+      <c r="B37" s="7"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A38" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E37" s="4" t="s">
+      <c r="E38" s="4" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A38" t="s">
-        <v>37</v>
-      </c>
-      <c r="B38" s="20">
-        <v>0</v>
-      </c>
-      <c r="C38" s="20">
-        <v>0</v>
-      </c>
-      <c r="E38" t="s">
-        <v>38</v>
-      </c>
-      <c r="F38" s="20">
-        <v>0</v>
-      </c>
-      <c r="G38" s="20">
-        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A39" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B39" s="20">
         <v>0</v>
@@ -1484,7 +1481,7 @@
         <v>0</v>
       </c>
       <c r="E39" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F39" s="20">
         <v>0</v>
@@ -1495,104 +1492,104 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A40" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40" s="20">
+        <v>0</v>
+      </c>
+      <c r="C40" s="20">
+        <v>0</v>
+      </c>
+      <c r="E40" t="s">
+        <v>40</v>
+      </c>
+      <c r="F40" s="20">
+        <v>0</v>
+      </c>
+      <c r="G40" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A41" t="s">
         <v>41</v>
       </c>
-      <c r="B40" s="20">
-        <v>0</v>
-      </c>
-      <c r="C40" s="20">
-        <v>0</v>
-      </c>
-      <c r="E40" t="s">
+      <c r="B41" s="20">
+        <v>0</v>
+      </c>
+      <c r="C41" s="20">
+        <v>0</v>
+      </c>
+      <c r="E41" t="s">
         <v>42</v>
       </c>
-      <c r="F40" s="20">
-        <v>0</v>
-      </c>
-      <c r="G40" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A41" s="11" t="s">
+      <c r="F41" s="20">
+        <v>0</v>
+      </c>
+      <c r="G41" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A42" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B41" s="12">
-        <f>SUM(B38:B40)</f>
-        <v>0</v>
-      </c>
-      <c r="C41" s="12">
-        <f>SUM(C38:C40)</f>
-        <v>0</v>
-      </c>
-      <c r="D41" s="4"/>
-      <c r="E41" s="11" t="s">
+      <c r="B42" s="12">
+        <f>SUM(B39:B41)</f>
+        <v>0</v>
+      </c>
+      <c r="C42" s="12">
+        <f>SUM(C39:C41)</f>
+        <v>0</v>
+      </c>
+      <c r="D42" s="4"/>
+      <c r="E42" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="F41" s="12">
-        <f>SUM(F38:F40)</f>
-        <v>0</v>
-      </c>
-      <c r="G41" s="12">
-        <f>SUM(G38:G40)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A42" s="28" t="s">
+      <c r="F42" s="12">
+        <f>SUM(F39:F41)</f>
+        <v>0</v>
+      </c>
+      <c r="G42" s="12">
+        <f>SUM(G39:G41)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A43" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="B42" s="28"/>
-      <c r="C42" s="28"/>
-      <c r="D42" s="28"/>
-      <c r="E42" s="28"/>
-      <c r="F42" s="10">
-        <f>F41-B41</f>
-        <v>0</v>
-      </c>
-      <c r="G42" s="10">
-        <f>G41-C41</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A43" s="7"/>
-      <c r="B43" s="7"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
+      <c r="B43" s="34"/>
+      <c r="C43" s="34"/>
+      <c r="D43" s="34"/>
+      <c r="E43" s="34"/>
+      <c r="F43" s="10">
+        <f>F42-B42</f>
+        <v>0</v>
+      </c>
+      <c r="G43" s="10">
+        <f>G42-C42</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="7"/>
+      <c r="B44" s="7"/>
+      <c r="C44" s="7"/>
+      <c r="D44" s="7"/>
+      <c r="E44" s="7"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A45" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E44" s="4" t="s">
+      <c r="E45" s="4" t="s">
         <v>45</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A45" t="s">
-        <v>46</v>
-      </c>
-      <c r="B45" s="20">
-        <v>0</v>
-      </c>
-      <c r="C45" s="20">
-        <v>0</v>
-      </c>
-      <c r="E45" t="s">
-        <v>47</v>
-      </c>
-      <c r="F45" s="20">
-        <v>0</v>
-      </c>
-      <c r="G45" s="20">
-        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A46" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B46" s="20">
         <v>0</v>
@@ -1601,7 +1598,7 @@
         <v>0</v>
       </c>
       <c r="E46" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F46" s="20">
         <v>0</v>
@@ -1612,7 +1609,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A47" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B47" s="20">
         <v>0</v>
@@ -1621,7 +1618,7 @@
         <v>0</v>
       </c>
       <c r="E47" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F47" s="20">
         <v>0</v>
@@ -1632,7 +1629,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A48" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B48" s="20">
         <v>0</v>
@@ -1641,7 +1638,7 @@
         <v>0</v>
       </c>
       <c r="E48" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F48" s="20">
         <v>0</v>
@@ -1652,97 +1649,97 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A49" t="s">
+        <v>52</v>
+      </c>
+      <c r="B49" s="20">
+        <v>0</v>
+      </c>
+      <c r="C49" s="20">
+        <v>0</v>
+      </c>
+      <c r="E49" t="s">
+        <v>53</v>
+      </c>
+      <c r="F49" s="20">
+        <v>0</v>
+      </c>
+      <c r="G49" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A50" t="s">
         <v>54</v>
       </c>
-      <c r="B49" s="20">
-        <v>0</v>
-      </c>
-      <c r="C49" s="20">
-        <v>0</v>
-      </c>
-      <c r="E49" t="s">
+      <c r="B50" s="20">
+        <v>0</v>
+      </c>
+      <c r="C50" s="20">
+        <v>0</v>
+      </c>
+      <c r="E50" t="s">
         <v>55</v>
       </c>
-      <c r="F49" s="20">
-        <v>0</v>
-      </c>
-      <c r="G49" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A50" s="11" t="s">
+      <c r="F50" s="20">
+        <v>0</v>
+      </c>
+      <c r="G50" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A51" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B50" s="12">
-        <f>SUM(B45:B49)</f>
-        <v>0</v>
-      </c>
-      <c r="C50" s="12">
-        <f>SUM(C45:C49)</f>
-        <v>0</v>
-      </c>
-      <c r="D50" s="4"/>
-      <c r="E50" s="11" t="s">
+      <c r="B51" s="12">
+        <f>SUM(B46:B50)</f>
+        <v>0</v>
+      </c>
+      <c r="C51" s="12">
+        <f>SUM(C46:C50)</f>
+        <v>0</v>
+      </c>
+      <c r="D51" s="4"/>
+      <c r="E51" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="F50" s="12">
-        <f>SUM(F45:F49)</f>
-        <v>0</v>
-      </c>
-      <c r="G50" s="12">
-        <f>SUM(G45:G49)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A51" s="28" t="s">
+      <c r="F51" s="12">
+        <f>SUM(F46:F50)</f>
+        <v>0</v>
+      </c>
+      <c r="G51" s="12">
+        <f>SUM(G46:G50)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A52" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="B51" s="28"/>
-      <c r="C51" s="28"/>
-      <c r="D51" s="28"/>
-      <c r="E51" s="28"/>
-      <c r="F51" s="10">
-        <f>F50-B50</f>
-        <v>0</v>
-      </c>
-      <c r="G51" s="10">
-        <f>G50-C50</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A53" s="4" t="s">
+      <c r="B52" s="34"/>
+      <c r="C52" s="34"/>
+      <c r="D52" s="34"/>
+      <c r="E52" s="34"/>
+      <c r="F52" s="10">
+        <f>F51-B51</f>
+        <v>0</v>
+      </c>
+      <c r="G52" s="10">
+        <f>G51-C51</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A54" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="E53" s="4" t="s">
+      <c r="E54" s="4" t="s">
         <v>58</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A54" t="s">
-        <v>10</v>
-      </c>
-      <c r="B54" s="20">
-        <v>0</v>
-      </c>
-      <c r="C54" s="20">
-        <v>0</v>
-      </c>
-      <c r="E54" t="s">
-        <v>59</v>
-      </c>
-      <c r="F54" s="20">
-        <v>0</v>
-      </c>
-      <c r="G54" s="20">
-        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A55" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B55" s="20">
         <v>0</v>
@@ -1751,7 +1748,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F55" s="20">
         <v>0</v>
@@ -1762,18 +1759,27 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A56" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B56" s="20">
         <v>0</v>
       </c>
       <c r="C56" s="20">
+        <v>0</v>
+      </c>
+      <c r="E56" t="s">
+        <v>60</v>
+      </c>
+      <c r="F56" s="20">
+        <v>0</v>
+      </c>
+      <c r="G56" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A57" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B57" s="20">
         <v>0</v>
@@ -1784,520 +1790,522 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A58" t="s">
+        <v>16</v>
+      </c>
+      <c r="B58" s="20">
+        <v>0</v>
+      </c>
+      <c r="C58" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A59" t="s">
         <v>54</v>
       </c>
-      <c r="B58" s="20">
-        <v>0</v>
-      </c>
-      <c r="C58" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A59" s="11" t="s">
+      <c r="B59" s="20">
+        <v>0</v>
+      </c>
+      <c r="C59" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A60" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B59" s="12">
-        <f>SUM(B54:B58)</f>
-        <v>0</v>
-      </c>
-      <c r="C59" s="12">
-        <f>SUM(C54:C58)</f>
-        <v>0</v>
-      </c>
-      <c r="D59" s="4"/>
-      <c r="E59" s="11" t="s">
+      <c r="B60" s="12">
+        <f>SUM(B55:B59)</f>
+        <v>0</v>
+      </c>
+      <c r="C60" s="12">
+        <f>SUM(C55:C59)</f>
+        <v>0</v>
+      </c>
+      <c r="D60" s="4"/>
+      <c r="E60" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="F59" s="12">
-        <f>SUM(F54:F55)</f>
-        <v>0</v>
-      </c>
-      <c r="G59" s="12">
-        <f>SUM(G54:G55)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A60" s="7"/>
-      <c r="E60" s="7"/>
+      <c r="F60" s="12">
+        <f>SUM(F55:F56)</f>
+        <v>0</v>
+      </c>
+      <c r="G60" s="12">
+        <f>SUM(G55:G56)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A61" s="4" t="s">
+      <c r="A61" s="7"/>
+      <c r="E61" s="7"/>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A62" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B61" s="12">
-        <f>B24+B34+B41+B50+B59</f>
-        <v>0</v>
-      </c>
-      <c r="C61" s="12">
-        <f>C24+C34+C41+C50+C59</f>
-        <v>0</v>
-      </c>
-      <c r="E61" s="4" t="s">
+      <c r="B62" s="12">
+        <f>B25+B35+B42+B51+B60</f>
+        <v>0</v>
+      </c>
+      <c r="C62" s="12">
+        <f>C25+C35+C42+C51+C60</f>
+        <v>0</v>
+      </c>
+      <c r="E62" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="F61" s="12">
-        <f>F24+F34+F41+F50+F59</f>
-        <v>0</v>
-      </c>
-      <c r="G61" s="12">
-        <f>G24+G34+G41+G50+G59</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A62" s="28" t="s">
+      <c r="F62" s="12">
+        <f>F25+F35+F42+F51+F60</f>
+        <v>0</v>
+      </c>
+      <c r="G62" s="12">
+        <f>G25+G35+G42+G51+G60</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A63" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="B62" s="28"/>
-      <c r="C62" s="28"/>
-      <c r="D62" s="28"/>
-      <c r="E62" s="28"/>
-      <c r="F62" s="10">
-        <f>F61-B61</f>
-        <v>0</v>
-      </c>
-      <c r="G62" s="10">
-        <f>G61-C61</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A63" s="28" t="s">
+      <c r="B63" s="34"/>
+      <c r="C63" s="34"/>
+      <c r="D63" s="34"/>
+      <c r="E63" s="34"/>
+      <c r="F63" s="10">
+        <f>F62-B62</f>
+        <v>0</v>
+      </c>
+      <c r="G63" s="10">
+        <f>G62-C62</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A64" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="B63" s="28"/>
-      <c r="C63" s="28"/>
-      <c r="D63" s="28"/>
-      <c r="E63" s="28"/>
-      <c r="F63" s="10">
-        <v>0</v>
-      </c>
-      <c r="G63" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A64" s="28" t="s">
+      <c r="B64" s="34"/>
+      <c r="C64" s="34"/>
+      <c r="D64" s="34"/>
+      <c r="E64" s="34"/>
+      <c r="F64" s="10">
+        <v>0</v>
+      </c>
+      <c r="G64" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A65" s="34" t="s">
         <v>64</v>
       </c>
-      <c r="B64" s="28"/>
-      <c r="C64" s="28"/>
-      <c r="D64" s="28"/>
-      <c r="E64" s="28"/>
-      <c r="F64" s="10">
-        <f>F62-F63</f>
-        <v>0</v>
-      </c>
-      <c r="G64" s="10">
-        <f>G62-G63</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A65" s="7"/>
-      <c r="B65" s="7"/>
-      <c r="C65" s="7"/>
-      <c r="D65" s="7"/>
-      <c r="E65" s="7"/>
+      <c r="B65" s="34"/>
+      <c r="C65" s="34"/>
+      <c r="D65" s="34"/>
+      <c r="E65" s="34"/>
+      <c r="F65" s="10">
+        <f>F63-F64</f>
+        <v>0</v>
+      </c>
+      <c r="G65" s="10">
+        <f>G63-G64</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A66" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" ht="32" x14ac:dyDescent="0.8">
-      <c r="A67" s="9" t="s">
+      <c r="A66" s="7"/>
+      <c r="B66" s="7"/>
+      <c r="C66" s="7"/>
+      <c r="D66" s="7"/>
+      <c r="E66" s="7"/>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A67" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="32" x14ac:dyDescent="0.8">
+      <c r="A68" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="B67" s="16">
-        <f>B12</f>
+      <c r="B68" s="16">
+        <f>B13</f>
+        <v>46387</v>
+      </c>
+      <c r="C68" s="16">
+        <f>C13</f>
         <v>46022</v>
       </c>
-      <c r="C67" s="16">
-        <f>C12</f>
-        <v>45657</v>
-      </c>
-      <c r="D67" s="5"/>
-      <c r="E67" s="9" t="s">
+      <c r="D68" s="5"/>
+      <c r="E68" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="F67" s="16">
-        <f>B12</f>
+      <c r="F68" s="16">
+        <f>B13</f>
+        <v>46387</v>
+      </c>
+      <c r="G68" s="16">
+        <f>C13</f>
         <v>46022</v>
-      </c>
-      <c r="G67" s="16">
-        <f>C12</f>
-        <v>45657</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="29.5" x14ac:dyDescent="0.75">
-      <c r="A68" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="B68" s="20">
-        <v>0</v>
-      </c>
-      <c r="C68" s="20">
-        <v>0</v>
-      </c>
-      <c r="E68" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="F68" s="20">
-        <v>0</v>
-      </c>
-      <c r="G68" s="20">
-        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="29.5" x14ac:dyDescent="0.75">
       <c r="A69" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B69" s="20">
+        <v>0</v>
+      </c>
+      <c r="C69" s="20">
+        <v>0</v>
+      </c>
+      <c r="E69" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="F69" s="20">
+        <v>0</v>
+      </c>
+      <c r="G69" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="29.5" x14ac:dyDescent="0.75">
+      <c r="A70" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="B69" s="20">
-        <v>0</v>
-      </c>
-      <c r="C69" s="20">
-        <v>0</v>
-      </c>
-      <c r="E69" s="8" t="s">
+      <c r="B70" s="20">
+        <v>0</v>
+      </c>
+      <c r="C70" s="20">
+        <v>0</v>
+      </c>
+      <c r="E70" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="F69" s="20">
-        <v>0</v>
-      </c>
-      <c r="G69" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A70" s="8" t="s">
+      <c r="F70" s="20">
+        <v>0</v>
+      </c>
+      <c r="G70" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A71" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="B70" s="20">
-        <v>0</v>
-      </c>
-      <c r="C70" s="20">
-        <v>0</v>
-      </c>
-      <c r="E70" s="8" t="s">
+      <c r="B71" s="20">
+        <v>0</v>
+      </c>
+      <c r="C71" s="20">
+        <v>0</v>
+      </c>
+      <c r="E71" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="F70" s="20">
-        <v>0</v>
-      </c>
-      <c r="G70" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" ht="29.5" x14ac:dyDescent="0.75">
-      <c r="A71" s="8" t="s">
+      <c r="F71" s="20">
+        <v>0</v>
+      </c>
+      <c r="G71" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="29.5" x14ac:dyDescent="0.75">
+      <c r="A72" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="B71" s="20">
-        <v>0</v>
-      </c>
-      <c r="C71" s="20">
-        <v>0</v>
-      </c>
-      <c r="E71" s="8" t="s">
+      <c r="B72" s="20">
+        <v>0</v>
+      </c>
+      <c r="C72" s="20">
+        <v>0</v>
+      </c>
+      <c r="E72" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="F71" s="20">
-        <v>0</v>
-      </c>
-      <c r="G71" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A72" s="11" t="s">
+      <c r="F72" s="20">
+        <v>0</v>
+      </c>
+      <c r="G72" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A73" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B72" s="12">
-        <f>SUM(B68:B71)</f>
-        <v>0</v>
-      </c>
-      <c r="C72" s="12">
-        <f>SUM(C68:C71)</f>
-        <v>0</v>
-      </c>
-      <c r="D72" s="4"/>
-      <c r="E72" s="11" t="s">
+      <c r="B73" s="12">
+        <f>SUM(B69:B72)</f>
+        <v>0</v>
+      </c>
+      <c r="C73" s="12">
+        <f>SUM(C69:C72)</f>
+        <v>0</v>
+      </c>
+      <c r="D73" s="4"/>
+      <c r="E73" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="F72" s="12">
-        <f>SUM(F68:F71)</f>
-        <v>0</v>
-      </c>
-      <c r="G72" s="12">
-        <f>SUM(G68:G71)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A73" s="28" t="s">
+      <c r="F73" s="12">
+        <f>SUM(F69:F72)</f>
+        <v>0</v>
+      </c>
+      <c r="G73" s="12">
+        <f>SUM(G69:G72)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A74" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="B73" s="28"/>
-      <c r="C73" s="28"/>
-      <c r="D73" s="28"/>
-      <c r="E73" s="28"/>
-      <c r="F73" s="10">
-        <v>0</v>
-      </c>
-      <c r="G73" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A74" s="28" t="s">
+      <c r="B74" s="34"/>
+      <c r="C74" s="34"/>
+      <c r="D74" s="34"/>
+      <c r="E74" s="34"/>
+      <c r="F74" s="10">
+        <v>0</v>
+      </c>
+      <c r="G74" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A75" s="34" t="s">
         <v>75</v>
       </c>
-      <c r="B74" s="28"/>
-      <c r="C74" s="28"/>
-      <c r="D74" s="28"/>
-      <c r="E74" s="28"/>
-      <c r="F74" s="10">
-        <f>F72-B72</f>
-        <v>0</v>
-      </c>
-      <c r="G74" s="10">
-        <f>G72-C72</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A75" s="7"/>
-      <c r="B75" s="7"/>
-      <c r="C75" s="7"/>
-      <c r="D75" s="7"/>
-      <c r="E75" s="7"/>
+      <c r="B75" s="34"/>
+      <c r="C75" s="34"/>
+      <c r="D75" s="34"/>
+      <c r="E75" s="34"/>
+      <c r="F75" s="10">
+        <f>F73-B73</f>
+        <v>0</v>
+      </c>
+      <c r="G75" s="10">
+        <f>G73-C73</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A76" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.8">
-      <c r="A77" s="31"/>
-      <c r="B77" s="31"/>
-      <c r="C77" s="31"/>
-      <c r="D77" s="31"/>
-      <c r="E77" s="31"/>
-      <c r="F77" s="17">
-        <f>B12</f>
+      <c r="A76" s="7"/>
+      <c r="B76" s="7"/>
+      <c r="C76" s="7"/>
+      <c r="D76" s="7"/>
+      <c r="E76" s="7"/>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A77" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.8">
+      <c r="A78" s="38"/>
+      <c r="B78" s="38"/>
+      <c r="C78" s="38"/>
+      <c r="D78" s="38"/>
+      <c r="E78" s="38"/>
+      <c r="F78" s="17">
+        <f>B13</f>
+        <v>46387</v>
+      </c>
+      <c r="G78" s="17">
+        <f>C13</f>
         <v>46022</v>
       </c>
-      <c r="G77" s="17">
-        <f>C12</f>
-        <v>45657</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A78" s="28" t="s">
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A79" s="34" t="s">
         <v>64</v>
       </c>
-      <c r="B78" s="28"/>
-      <c r="C78" s="28"/>
-      <c r="D78" s="28"/>
-      <c r="E78" s="28"/>
-      <c r="F78" s="10">
-        <f>F64</f>
-        <v>0</v>
-      </c>
-      <c r="G78" s="10">
-        <f>G64</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A79" s="28" t="s">
+      <c r="B79" s="34"/>
+      <c r="C79" s="34"/>
+      <c r="D79" s="34"/>
+      <c r="E79" s="34"/>
+      <c r="F79" s="10">
+        <f>F65</f>
+        <v>0</v>
+      </c>
+      <c r="G79" s="10">
+        <f>G65</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A80" s="34" t="s">
         <v>75</v>
       </c>
-      <c r="B79" s="28"/>
-      <c r="C79" s="28"/>
-      <c r="D79" s="28"/>
-      <c r="E79" s="28"/>
-      <c r="F79" s="10">
-        <f>F74</f>
-        <v>0</v>
-      </c>
-      <c r="G79" s="10">
-        <f>G74</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A80" s="28" t="s">
+      <c r="B80" s="34"/>
+      <c r="C80" s="34"/>
+      <c r="D80" s="34"/>
+      <c r="E80" s="34"/>
+      <c r="F80" s="10">
+        <f>F75</f>
+        <v>0</v>
+      </c>
+      <c r="G80" s="10">
+        <f>G75</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A81" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="B80" s="28"/>
-      <c r="C80" s="28"/>
-      <c r="D80" s="28"/>
-      <c r="E80" s="28"/>
-      <c r="F80" s="10">
-        <f>F78+F79-F73</f>
-        <v>0</v>
-      </c>
-      <c r="G80" s="10">
-        <f>G78+G79-G73</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.75">
-      <c r="A81" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" ht="16" x14ac:dyDescent="0.8">
-      <c r="A83" s="33" t="s">
+      <c r="B81" s="34"/>
+      <c r="C81" s="34"/>
+      <c r="D81" s="34"/>
+      <c r="E81" s="34"/>
+      <c r="F81" s="10">
+        <f>F79+F80-F74</f>
+        <v>0</v>
+      </c>
+      <c r="G81" s="10">
+        <f>G79+G80-G74</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A82" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="16" x14ac:dyDescent="0.8">
+      <c r="A84" s="35" t="s">
         <v>77</v>
       </c>
-      <c r="B83" s="33"/>
-      <c r="C83" s="33"/>
-      <c r="D83" s="33"/>
-      <c r="E83" s="33"/>
-      <c r="F83" s="17">
-        <f>B12</f>
+      <c r="B84" s="35"/>
+      <c r="C84" s="35"/>
+      <c r="D84" s="35"/>
+      <c r="E84" s="35"/>
+      <c r="F84" s="17">
+        <f>B13</f>
+        <v>46387</v>
+      </c>
+      <c r="G84" s="17">
+        <f>C13</f>
         <v>46022</v>
       </c>
-      <c r="G83" s="17">
-        <f>C12</f>
-        <v>45657</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.75">
-      <c r="A84" s="30" t="s">
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A85" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="B84" s="30"/>
-      <c r="C84" s="30"/>
-      <c r="D84" s="30"/>
-      <c r="E84" s="30"/>
-      <c r="F84" s="20">
-        <v>0</v>
-      </c>
-      <c r="G84" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.75">
-      <c r="A85" s="30" t="s">
+      <c r="B85" s="36"/>
+      <c r="C85" s="36"/>
+      <c r="D85" s="36"/>
+      <c r="E85" s="36"/>
+      <c r="F85" s="20">
+        <v>0</v>
+      </c>
+      <c r="G85" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A86" s="36" t="s">
         <v>79</v>
       </c>
-      <c r="B85" s="30"/>
-      <c r="C85" s="30"/>
-      <c r="D85" s="30"/>
-      <c r="E85" s="30"/>
-      <c r="F85" s="20">
-        <v>0</v>
-      </c>
-      <c r="G85" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" ht="16" x14ac:dyDescent="0.8">
-      <c r="A88" s="6" t="s">
+      <c r="B86" s="36"/>
+      <c r="C86" s="36"/>
+      <c r="D86" s="36"/>
+      <c r="E86" s="36"/>
+      <c r="F86" s="20">
+        <v>0</v>
+      </c>
+      <c r="G86" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" ht="16" x14ac:dyDescent="0.8">
+      <c r="A89" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B88" s="17">
-        <f>B12</f>
+      <c r="B89" s="17">
+        <f>B13</f>
+        <v>46387</v>
+      </c>
+      <c r="C89" s="17">
+        <f>C13</f>
         <v>46022</v>
       </c>
-      <c r="C88" s="17">
-        <f>C12</f>
-        <v>45657</v>
-      </c>
-      <c r="E88" s="6" t="s">
+      <c r="E89" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F88" s="17">
-        <f>B12</f>
+      <c r="F89" s="17">
+        <f>B13</f>
+        <v>46387</v>
+      </c>
+      <c r="G89" s="17">
+        <f>C13</f>
         <v>46022</v>
       </c>
-      <c r="G88" s="17">
-        <f>C12</f>
-        <v>45657</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.75">
-      <c r="A89" t="s">
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A90" t="s">
         <v>3</v>
       </c>
-      <c r="B89" s="10">
-        <v>0</v>
-      </c>
-      <c r="C89" s="10">
-        <v>0</v>
-      </c>
-      <c r="E89" t="s">
+      <c r="B90" s="10">
+        <v>0</v>
+      </c>
+      <c r="C90" s="10">
+        <v>0</v>
+      </c>
+      <c r="E90" t="s">
         <v>3</v>
       </c>
-      <c r="F89" s="10">
-        <v>0</v>
-      </c>
-      <c r="G89" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.75">
-      <c r="A90" t="s">
+      <c r="F90" s="10">
+        <v>0</v>
+      </c>
+      <c r="G90" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A91" t="s">
         <v>4</v>
       </c>
-      <c r="B90" s="10">
-        <v>0</v>
-      </c>
-      <c r="C90" s="10">
-        <v>0</v>
-      </c>
-      <c r="E90" t="s">
+      <c r="B91" s="10">
+        <v>0</v>
+      </c>
+      <c r="C91" s="10">
+        <v>0</v>
+      </c>
+      <c r="E91" t="s">
         <v>4</v>
       </c>
-      <c r="F90" s="10">
-        <v>0</v>
-      </c>
-      <c r="G90" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.75">
-      <c r="A91" s="11" t="s">
+      <c r="F91" s="10">
+        <v>0</v>
+      </c>
+      <c r="G91" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A92" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B91" s="12">
-        <f>SUM(B89:B90)</f>
-        <v>0</v>
-      </c>
-      <c r="C91" s="12">
-        <f>SUM(C89:C90)</f>
-        <v>0</v>
-      </c>
-      <c r="D91" s="4"/>
-      <c r="E91" s="11" t="s">
+      <c r="B92" s="12">
+        <f>SUM(B90:B91)</f>
+        <v>0</v>
+      </c>
+      <c r="C92" s="12">
+        <f>SUM(C90:C91)</f>
+        <v>0</v>
+      </c>
+      <c r="D92" s="4"/>
+      <c r="E92" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="F91" s="12">
-        <f>SUM(F89:F90)</f>
-        <v>0</v>
-      </c>
-      <c r="G91" s="12">
-        <f>SUM(G89:G90)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.75">
-      <c r="A92" s="11"/>
-      <c r="B92" s="12"/>
-      <c r="C92" s="12"/>
-      <c r="D92" s="4"/>
-      <c r="E92" s="11"/>
-      <c r="F92" s="12"/>
-      <c r="G92" s="12"/>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.75">
+      <c r="F92" s="12">
+        <f>SUM(F90:F91)</f>
+        <v>0</v>
+      </c>
+      <c r="G92" s="12">
+        <f>SUM(G90:G91)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A93" s="11"/>
       <c r="B93" s="12"/>
       <c r="C93" s="12"/>
@@ -2306,274 +2314,310 @@
       <c r="F93" s="12"/>
       <c r="G93" s="12"/>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.75">
-      <c r="C96" s="1"/>
-      <c r="D96" s="1"/>
-      <c r="H96" s="1"/>
-      <c r="I96" s="1"/>
-    </row>
-    <row r="98" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A98" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="B98" s="5"/>
-    </row>
-    <row r="99" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A99" s="13" t="s">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A94" s="11"/>
+      <c r="B94" s="12"/>
+      <c r="C94" s="12"/>
+      <c r="D94" s="4"/>
+      <c r="E94" s="11"/>
+      <c r="F94" s="12"/>
+      <c r="G94" s="12"/>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.75">
+      <c r="C97" s="1"/>
+      <c r="D97" s="1"/>
+      <c r="H97" s="1"/>
+      <c r="I97" s="1"/>
+    </row>
+    <row r="99" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A99" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B99" s="5"/>
+    </row>
+    <row r="100" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A100" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="B99" s="14">
-        <f>G84+G85</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A100" s="13" t="s">
+      <c r="B100" s="14">
+        <f>G85+G86</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A101" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="B100" s="14">
-        <f>F80</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A101" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B101" s="25">
-        <f>SUM(B99:B100)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A102" s="13" t="s">
+      <c r="B101" s="14">
+        <f>F81</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A102" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B102" s="25">
+        <f>SUM(B100:B101)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A103" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="B102" s="14">
-        <f>F84+F85</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A103" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="B103" s="25">
-        <f>B101-B102</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A104" s="15" t="s">
+      <c r="B103" s="14">
+        <f>F85+F86</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A104" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B104" s="25">
+        <f>B102-B103</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A105" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="B104" s="32" t="str">
-        <f>IF(B103=0,"Quadratura OK","Errore quadratura")</f>
+      <c r="B105" s="33" t="str">
+        <f>IF(B104=0,"Quadratura OK","Errore quadratura")</f>
         <v>Quadratura OK</v>
       </c>
-      <c r="C104" s="32"/>
-      <c r="D104" s="13"/>
-      <c r="E104" s="13"/>
-      <c r="F104" s="13"/>
-      <c r="G104" s="13"/>
-    </row>
-    <row r="107" spans="1:7" ht="16" x14ac:dyDescent="0.8">
-      <c r="A107" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="B107" s="13"/>
-    </row>
-    <row r="108" spans="1:7" ht="16" x14ac:dyDescent="0.8">
-      <c r="A108" s="13" t="s">
-        <v>108</v>
+      <c r="C105" s="33"/>
+      <c r="D105" s="13"/>
+      <c r="E105" s="13"/>
+      <c r="F105" s="13"/>
+      <c r="G105" s="13"/>
+    </row>
+    <row r="108" spans="1:9" ht="16" x14ac:dyDescent="0.8">
+      <c r="A108" s="5" t="s">
+        <v>104</v>
       </c>
       <c r="B108" s="13"/>
     </row>
-    <row r="109" spans="1:7" ht="16" x14ac:dyDescent="0.8">
+    <row r="109" spans="1:9" ht="16" x14ac:dyDescent="0.8">
       <c r="A109" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="B109" s="13"/>
+    </row>
+    <row r="110" spans="1:9" ht="16" x14ac:dyDescent="0.8">
+      <c r="A110" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="B110" s="13"/>
+    </row>
+    <row r="111" spans="1:9" ht="16" x14ac:dyDescent="0.8">
+      <c r="A111" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="B109" s="13"/>
-    </row>
-    <row r="110" spans="1:7" ht="16" x14ac:dyDescent="0.8">
-      <c r="A110" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="B110" s="13"/>
-    </row>
-    <row r="111" spans="1:7" ht="16" x14ac:dyDescent="0.8">
       <c r="B111" s="13"/>
     </row>
-    <row r="112" spans="1:7" ht="16" x14ac:dyDescent="0.8">
-      <c r="A112" s="13"/>
+    <row r="112" spans="1:9" ht="16" x14ac:dyDescent="0.8">
       <c r="B112" s="13"/>
     </row>
     <row r="113" spans="1:2" ht="16" x14ac:dyDescent="0.8">
-      <c r="A113" s="13" t="s">
-        <v>94</v>
-      </c>
+      <c r="A113" s="13"/>
       <c r="B113" s="13"/>
     </row>
     <row r="114" spans="1:2" ht="16" x14ac:dyDescent="0.8">
       <c r="A114" s="13" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="B114" s="13"/>
     </row>
     <row r="115" spans="1:2" ht="16" x14ac:dyDescent="0.8">
-      <c r="A115" s="27" t="s">
+      <c r="A115" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B115" s="13"/>
+    </row>
+    <row r="116" spans="1:2" ht="16" x14ac:dyDescent="0.8">
+      <c r="A116" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="B115" s="13"/>
-    </row>
-    <row r="116" spans="1:2" ht="16" x14ac:dyDescent="0.8">
-      <c r="A116" s="26" t="s">
-        <v>100</v>
-      </c>
       <c r="B116" s="13"/>
     </row>
     <row r="117" spans="1:2" ht="16" x14ac:dyDescent="0.8">
-      <c r="A117" s="26"/>
+      <c r="A117" s="26" t="s">
+        <v>99</v>
+      </c>
       <c r="B117" s="13"/>
     </row>
     <row r="118" spans="1:2" ht="16" x14ac:dyDescent="0.8">
       <c r="A118" s="26"/>
       <c r="B118" s="13"/>
     </row>
-    <row r="119" spans="1:2" s="23" customFormat="1" ht="16" x14ac:dyDescent="0.8">
-      <c r="A119" s="37" t="s">
+    <row r="119" spans="1:2" s="30" customFormat="1" ht="16" x14ac:dyDescent="0.8">
+      <c r="A119" s="28"/>
+      <c r="B119" s="29"/>
+    </row>
+    <row r="120" spans="1:2" s="30" customFormat="1" ht="16" x14ac:dyDescent="0.8">
+      <c r="A120" s="31" t="s">
+        <v>115</v>
+      </c>
+      <c r="B120" s="29"/>
+    </row>
+    <row r="121" spans="1:2" s="30" customFormat="1" ht="16" x14ac:dyDescent="0.8">
+      <c r="A121" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="B121" s="29"/>
+    </row>
+    <row r="122" spans="1:2" s="30" customFormat="1" ht="16" x14ac:dyDescent="0.8">
+      <c r="A122" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="B122" s="29"/>
+    </row>
+    <row r="123" spans="1:2" s="30" customFormat="1" ht="16" x14ac:dyDescent="0.8">
+      <c r="A123" s="27"/>
+      <c r="B123" s="29"/>
+    </row>
+    <row r="124" spans="1:2" s="30" customFormat="1" ht="16" x14ac:dyDescent="0.8">
+      <c r="A124" s="28"/>
+      <c r="B124" s="29"/>
+    </row>
+    <row r="125" spans="1:2" s="23" customFormat="1" ht="16" x14ac:dyDescent="0.8">
+      <c r="A125" s="31" t="s">
+        <v>111</v>
+      </c>
+      <c r="B125" s="32"/>
+    </row>
+    <row r="126" spans="1:2" s="30" customFormat="1" ht="16" x14ac:dyDescent="0.8">
+      <c r="A126" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="B126" s="29"/>
+    </row>
+    <row r="127" spans="1:2" s="30" customFormat="1" ht="16" x14ac:dyDescent="0.8">
+      <c r="A127" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="B127" s="29"/>
+    </row>
+    <row r="128" spans="1:2" ht="16" x14ac:dyDescent="0.8">
+      <c r="A128" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="B119" s="38"/>
-    </row>
-    <row r="120" spans="1:2" s="36" customFormat="1" ht="16" x14ac:dyDescent="0.8">
-      <c r="A120" s="34" t="s">
-        <v>110</v>
-      </c>
-      <c r="B120" s="35"/>
-    </row>
-    <row r="121" spans="1:2" s="36" customFormat="1" ht="16" x14ac:dyDescent="0.8">
-      <c r="A121" s="34" t="s">
-        <v>111</v>
-      </c>
-      <c r="B121" s="35"/>
-    </row>
-    <row r="122" spans="1:2" ht="16" x14ac:dyDescent="0.8">
-      <c r="A122" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="B122" s="13"/>
-    </row>
-    <row r="123" spans="1:2" ht="16" x14ac:dyDescent="0.8">
-      <c r="A123" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="B123" s="13"/>
-    </row>
-    <row r="124" spans="1:2" ht="16" x14ac:dyDescent="0.8">
-      <c r="A124" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="B124" s="13"/>
-    </row>
-    <row r="125" spans="1:2" ht="16" x14ac:dyDescent="0.8">
-      <c r="A125" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="B125" s="13"/>
-    </row>
-    <row r="126" spans="1:2" ht="16" x14ac:dyDescent="0.8">
-      <c r="A126" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="B126" s="13"/>
-    </row>
-    <row r="127" spans="1:2" ht="16" x14ac:dyDescent="0.8">
-      <c r="A127" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="B127" s="13"/>
-    </row>
-    <row r="128" spans="1:2" ht="16" x14ac:dyDescent="0.8">
-      <c r="A128" s="13"/>
       <c r="B128" s="13"/>
     </row>
     <row r="129" spans="1:2" ht="16" x14ac:dyDescent="0.8">
       <c r="A129" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="B129" s="13"/>
+    </row>
+    <row r="130" spans="1:2" ht="16" x14ac:dyDescent="0.8">
+      <c r="A130" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="B130" s="13"/>
+    </row>
+    <row r="131" spans="1:2" ht="16" x14ac:dyDescent="0.8">
+      <c r="A131" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="B131" s="13"/>
+    </row>
+    <row r="132" spans="1:2" ht="16" x14ac:dyDescent="0.8">
+      <c r="A132" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="B132" s="13"/>
+    </row>
+    <row r="133" spans="1:2" ht="16" x14ac:dyDescent="0.8">
+      <c r="A133" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="B133" s="13"/>
+    </row>
+    <row r="134" spans="1:2" ht="16" x14ac:dyDescent="0.8">
+      <c r="A134" s="13"/>
+      <c r="B134" s="13"/>
+    </row>
+    <row r="135" spans="1:2" ht="16" x14ac:dyDescent="0.8">
+      <c r="A135" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="B129" s="13"/>
-    </row>
-    <row r="130" spans="1:2" ht="16" x14ac:dyDescent="0.8">
-      <c r="A130" s="26" t="s">
+      <c r="B135" s="13"/>
+    </row>
+    <row r="136" spans="1:2" ht="16" x14ac:dyDescent="0.8">
+      <c r="A136" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="B130" s="13"/>
-    </row>
-    <row r="131" spans="1:2" ht="16" x14ac:dyDescent="0.8">
-      <c r="A131" s="13"/>
-      <c r="B131" s="13"/>
-    </row>
-    <row r="132" spans="1:2" ht="16" x14ac:dyDescent="0.8">
-      <c r="A132" s="13"/>
-      <c r="B132" s="13"/>
-    </row>
-    <row r="133" spans="1:2" ht="16" x14ac:dyDescent="0.8">
-      <c r="A133" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="B133" s="13"/>
+      <c r="B136" s="13"/>
+    </row>
+    <row r="137" spans="1:2" ht="16" x14ac:dyDescent="0.8">
+      <c r="A137" s="13"/>
+      <c r="B137" s="13"/>
+    </row>
+    <row r="138" spans="1:2" ht="16" x14ac:dyDescent="0.8">
+      <c r="A138" s="13"/>
+      <c r="B138" s="13"/>
+    </row>
+    <row r="139" spans="1:2" ht="16" x14ac:dyDescent="0.8">
+      <c r="A139" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="B139" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B104:C104"/>
     <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A63:E63"/>
+    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A74:E74"/>
+    <mergeCell ref="A75:E75"/>
+    <mergeCell ref="A78:E78"/>
+    <mergeCell ref="B105:C105"/>
     <mergeCell ref="A80:E80"/>
-    <mergeCell ref="A83:E83"/>
+    <mergeCell ref="A81:E81"/>
     <mergeCell ref="A84:E84"/>
     <mergeCell ref="A85:E85"/>
-    <mergeCell ref="A78:E78"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="A51:E51"/>
-    <mergeCell ref="A62:E62"/>
-    <mergeCell ref="A63:E63"/>
-    <mergeCell ref="A64:E64"/>
-    <mergeCell ref="A73:E73"/>
-    <mergeCell ref="A74:E74"/>
-    <mergeCell ref="A77:E77"/>
+    <mergeCell ref="A86:E86"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
-  <conditionalFormatting sqref="A104:C104">
+  <conditionalFormatting sqref="A105:C105">
     <cfRule type="expression" dxfId="2" priority="1">
-      <formula>$B$104="Quadratura OK"</formula>
+      <formula>$B$105="Quadratura OK"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$B$104="Errore quadratura"</formula>
+      <formula>$B$105="Errore quadratura"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B14:C18 F14:G23 B28:C32 F28:G33 B38:C40 F38:G40 B45:C49 F45:G49 F54:G55 B54:C58 F63:G63 B68:C71 F68:G71 F73:G73 F78:G80 F84:G85 B89:C90 F89:G90">
+  <conditionalFormatting sqref="B15:C19 F15:G24 B29:C33 F29:G34 B39:C41 F39:G41 B46:C50 F46:G50 F55:G56 B55:C59 F64:G64 B69:C72 F69:G72 F74:G74 F79:G81 F85:G86 B90:C91 F90:G91">
     <cfRule type="expression" dxfId="0" priority="4">
-      <formula>UPPER(TRIM($B$4))="SI"</formula>
+      <formula>UPPER(TRIM($B$5))="SI"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="B4" xr:uid="{79B1FB1E-D2E6-4372-8C9B-16A9C050BFAD}">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="B5" xr:uid="{79B1FB1E-D2E6-4372-8C9B-16A9C050BFAD}">
       <formula1>"Si,No"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="A127" r:id="rId1" tooltip="https://www.banana.ch/apps/it/it/contabilita-terzo-settore/fino-a-300000" xr:uid="{A59A2887-F854-9A4D-8B4D-BE6E12243749}"/>
-    <hyperlink ref="A130" r:id="rId2" tooltip="https://www.banana.ch/it/node/9249" xr:uid="{B43AA590-682D-AE46-850F-5944AE67B430}"/>
-    <hyperlink ref="A115" r:id="rId3" xr:uid="{3790B8D1-CB6E-46EF-89B8-9A24475ADEDA}"/>
-    <hyperlink ref="A116" r:id="rId4" xr:uid="{FAAD52DE-39AC-4ADB-93B1-F7F1CB7B8A23}"/>
+    <hyperlink ref="A133" r:id="rId1" tooltip="https://www.banana.ch/apps/it/it/contabilita-terzo-settore/fino-a-300000" xr:uid="{A59A2887-F854-9A4D-8B4D-BE6E12243749}"/>
+    <hyperlink ref="A136" r:id="rId2" tooltip="https://www.banana.ch/it/node/9249" xr:uid="{B43AA590-682D-AE46-850F-5944AE67B430}"/>
+    <hyperlink ref="A116" r:id="rId3" xr:uid="{3790B8D1-CB6E-46EF-89B8-9A24475ADEDA}"/>
+    <hyperlink ref="A117" r:id="rId4" xr:uid="{FAAD52DE-39AC-4ADB-93B1-F7F1CB7B8A23}"/>
+    <hyperlink ref="A122" r:id="rId5" xr:uid="{D19CD639-7985-436E-98CA-F59FE337A4D4}"/>
   </hyperlinks>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="51" fitToWidth="0" fitToHeight="0" orientation="portrait" r:id="rId5"/>
+  <pageSetup paperSize="9" scale="51" fitToWidth="0" fitToHeight="0" orientation="portrait" r:id="rId6"/>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="97" max="6" man="1"/>
+    <brk id="98" max="6" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>